--- a/artfynd/A 37166-2024 artfynd.xlsx
+++ b/artfynd/A 37166-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681121</v>
+        <v>121681335</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576708</v>
+        <v>576701</v>
       </c>
       <c r="R2" t="n">
-        <v>6654465</v>
+        <v>6654461</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681335</v>
+        <v>121681121</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576701</v>
+        <v>576708</v>
       </c>
       <c r="R3" t="n">
-        <v>6654461</v>
+        <v>6654465</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 37166-2024 artfynd.xlsx
+++ b/artfynd/A 37166-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681335</v>
+        <v>121681121</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576701</v>
+        <v>576708</v>
       </c>
       <c r="R2" t="n">
-        <v>6654461</v>
+        <v>6654465</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681121</v>
+        <v>121681335</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576708</v>
+        <v>576701</v>
       </c>
       <c r="R3" t="n">
-        <v>6654465</v>
+        <v>6654461</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 37166-2024 artfynd.xlsx
+++ b/artfynd/A 37166-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681335</v>
+        <v>121681121</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576701</v>
+        <v>576708</v>
       </c>
       <c r="R2" t="n">
-        <v>6654461</v>
+        <v>6654465</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681121</v>
+        <v>121681335</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576708</v>
+        <v>576701</v>
       </c>
       <c r="R3" t="n">
-        <v>6654465</v>
+        <v>6654461</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 37166-2024 artfynd.xlsx
+++ b/artfynd/A 37166-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681121</v>
       </c>
       <c r="B2" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>121681335</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 37166-2024 artfynd.xlsx
+++ b/artfynd/A 37166-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681121</v>
+        <v>121681335</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576708</v>
+        <v>576701</v>
       </c>
       <c r="R2" t="n">
-        <v>6654465</v>
+        <v>6654461</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681335</v>
+        <v>121681121</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576701</v>
+        <v>576708</v>
       </c>
       <c r="R3" t="n">
-        <v>6654461</v>
+        <v>6654465</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 37166-2024 artfynd.xlsx
+++ b/artfynd/A 37166-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681335</v>
       </c>
       <c r="B2" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>121681121</v>
       </c>
       <c r="B3" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 37166-2024 artfynd.xlsx
+++ b/artfynd/A 37166-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681335</v>
+        <v>121680834</v>
       </c>
       <c r="B2" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576701</v>
+        <v>576715</v>
       </c>
       <c r="R2" t="n">
-        <v>6654461</v>
+        <v>6654542</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,47 +795,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681121</v>
+        <v>121680963</v>
       </c>
       <c r="B3" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576708</v>
+        <v>576716</v>
       </c>
       <c r="R3" t="n">
-        <v>6654465</v>
+        <v>6654547</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,740 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Diana Rubene</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121680962</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ljusberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>576684</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6654446</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Diana Rubene</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121680968</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jordbron, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576622</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6654530</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Diana Rubene</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121681121</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ljusberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>576708</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6654465</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Signe Vendike</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121681122</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ljusberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576703</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6654448</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121681123</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jordbron, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576633</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6654535</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121681335</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ljusberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>576701</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6654461</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Diana Rubene</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Rejlers - Sala till Avesta</t>
         </is>

--- a/artfynd/A 37166-2024 artfynd.xlsx
+++ b/artfynd/A 37166-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121680834</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121680963</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,6 +1057,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121680962</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1167,6 +1187,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121680968</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1287,6 +1312,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681121</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1407,6 +1437,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681122</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1527,6 +1562,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681123</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1647,8 +1687,23 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681335</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>